--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -877,7 +877,7 @@
     <t>0.0153,0.9764,0.0028,0.0036</t>
   </si>
   <si>
-    <t>0.0359,0.9218,0.0014,0.0116</t>
+    <t>0.0359,0.9218,0.0014,0.0115</t>
   </si>
   <si>
     <t>0.0107,0.9743,0.0021,0.0063</t>
@@ -913,7 +913,7 @@
     <t>0.9154,0.0462,0.0111,0.0043</t>
   </si>
   <si>
-    <t>0.5032,0.3039,0.0054,0.0266</t>
+    <t>0.5032,0.3039,0.0054,0.0265</t>
   </si>
   <si>
     <t>0.0148,0.0003,0.9827,0.0018</t>
@@ -955,7 +955,7 @@
     <t>0.0188,0.0121,0.9751,0.0015</t>
   </si>
   <si>
-    <t>0.0365,0.6590,0.0026,0.4044</t>
+    <t>0.0365,0.6590,0.0026,0.4045</t>
   </si>
   <si>
     <t>0.0001,0.9998,0.0003,0.0001</t>
@@ -1033,7 +1033,7 @@
     <t>0.6023,0.1723,0.1019,0.0115</t>
   </si>
   <si>
-    <t>0.4454,0.0079,0.5350,0.0026</t>
+    <t>0.4454,0.0079,0.5351,0.0026</t>
   </si>
   <si>
     <t>0.0020,0.9388,0.9098,0.0006</t>
@@ -1249,7 +1249,7 @@
     <t>0.8939,0.0257,0.0629,0.0041</t>
   </si>
   <si>
-    <t>0.6366,0.0021,0.0004,0.4816</t>
+    <t>0.6365,0.0021,0.0004,0.4816</t>
   </si>
   <si>
     <t>0.0027,0.0198,0.0002,0.9984</t>
@@ -1555,7 +1555,7 @@
     <t>0.0132,0.0073,0.9848,0.0004</t>
   </si>
   <si>
-    <t>0.2057,0.0550,0.7468,0.0034</t>
+    <t>0.2056,0.0550,0.7468,0.0034</t>
   </si>
   <si>
     <t>0.0551,0.0013,0.9547,0.0007</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="526">
   <si>
     <t>Filename</t>
   </si>
@@ -811,31 +811,37 @@
     <t>1,0,0,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,0</t>
   </si>
   <si>
     <t>0,0,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,1,0</t>
   </si>
   <si>
     <t>0,0,0,1</t>
   </si>
   <si>
-    <t>0.9747,0.0090,0.0071,0.0014</t>
-  </si>
-  <si>
-    <t>0.4567,0.0131,0.0004,0.4544</t>
-  </si>
-  <si>
-    <t>0.9264,0.0112,0.0012,0.0176</t>
-  </si>
-  <si>
-    <t>0.8576,0.0035,0.0007,0.0955</t>
-  </si>
-  <si>
-    <t>0.9818,0.0026,0.0012,0.0055</t>
+    <t>0.9746,0.0091,0.0071,0.0014</t>
+  </si>
+  <si>
+    <t>0.4556,0.0131,0.0004,0.4559</t>
+  </si>
+  <si>
+    <t>0.9261,0.0112,0.0012,0.0177</t>
+  </si>
+  <si>
+    <t>0.8571,0.0035,0.0007,0.0961</t>
+  </si>
+  <si>
+    <t>0.9817,0.0026,0.0012,0.0056</t>
   </si>
   <si>
     <t>0.9848,0.0026,0.0013,0.0038</t>
@@ -844,118 +850,118 @@
     <t>0.9835,0.0016,0.0026,0.0040</t>
   </si>
   <si>
-    <t>0.9399,0.0005,0.0003,0.0614</t>
-  </si>
-  <si>
-    <t>0.8892,0.0356,0.0002,0.0048</t>
+    <t>0.9396,0.0005,0.0003,0.0619</t>
+  </si>
+  <si>
+    <t>0.8888,0.0357,0.0002,0.0048</t>
   </si>
   <si>
     <t>0.9776,0.0066,0.0011,0.0042</t>
   </si>
   <si>
-    <t>0.9825,0.0009,0.0008,0.0074</t>
+    <t>0.9824,0.0009,0.0008,0.0075</t>
   </si>
   <si>
     <t>0.9928,0.0009,0.0017,0.0013</t>
   </si>
   <si>
-    <t>0.9583,0.0072,0.0242,0.0007</t>
-  </si>
-  <si>
-    <t>0.3697,0.1819,0.2203,0.0154</t>
-  </si>
-  <si>
-    <t>0.7908,0.0041,0.2378,0.0003</t>
-  </si>
-  <si>
-    <t>0.5120,0.0222,0.4685,0.0027</t>
-  </si>
-  <si>
-    <t>0.9367,0.0045,0.0575,0.0014</t>
+    <t>0.9582,0.0072,0.0242,0.0007</t>
+  </si>
+  <si>
+    <t>0.3693,0.1820,0.2205,0.0155</t>
+  </si>
+  <si>
+    <t>0.7906,0.0041,0.2381,0.0003</t>
+  </si>
+  <si>
+    <t>0.5118,0.0222,0.4689,0.0027</t>
+  </si>
+  <si>
+    <t>0.9366,0.0045,0.0577,0.0015</t>
   </si>
   <si>
     <t>0.0153,0.9764,0.0028,0.0036</t>
   </si>
   <si>
-    <t>0.0359,0.9218,0.0014,0.0115</t>
+    <t>0.0358,0.9218,0.0014,0.0116</t>
   </si>
   <si>
     <t>0.0107,0.9743,0.0021,0.0063</t>
   </si>
   <si>
-    <t>0.0471,0.8665,0.0022,0.0332</t>
+    <t>0.0469,0.8665,0.0022,0.0334</t>
   </si>
   <si>
     <t>0.0024,0.9968,0.0067,0.0010</t>
   </si>
   <si>
-    <t>0.9365,0.0032,0.0640,0.0008</t>
-  </si>
-  <si>
-    <t>0.4361,0.0558,0.4969,0.0121</t>
-  </si>
-  <si>
-    <t>0.1896,0.0008,0.8773,0.0003</t>
-  </si>
-  <si>
-    <t>0.4311,0.0111,0.6255,0.0019</t>
-  </si>
-  <si>
-    <t>0.5382,0.0091,0.5312,0.0033</t>
-  </si>
-  <si>
-    <t>0.2863,0.0015,0.7951,0.0006</t>
-  </si>
-  <si>
-    <t>0.0403,0.0004,0.9703,0.0002</t>
-  </si>
-  <si>
-    <t>0.9154,0.0462,0.0111,0.0043</t>
-  </si>
-  <si>
-    <t>0.5032,0.3039,0.0054,0.0265</t>
+    <t>0.9364,0.0033,0.0641,0.0008</t>
+  </si>
+  <si>
+    <t>0.4359,0.0558,0.4971,0.0122</t>
+  </si>
+  <si>
+    <t>0.1895,0.0008,0.8774,0.0003</t>
+  </si>
+  <si>
+    <t>0.4305,0.0111,0.6261,0.0020</t>
+  </si>
+  <si>
+    <t>0.5377,0.0091,0.5318,0.0033</t>
+  </si>
+  <si>
+    <t>0.2860,0.0015,0.7954,0.0006</t>
+  </si>
+  <si>
+    <t>0.0402,0.0004,0.9703,0.0002</t>
+  </si>
+  <si>
+    <t>0.9152,0.0463,0.0111,0.0044</t>
+  </si>
+  <si>
+    <t>0.5025,0.3040,0.0055,0.0267</t>
   </si>
   <si>
     <t>0.0148,0.0003,0.9827,0.0018</t>
   </si>
   <si>
-    <t>0.4683,0.1165,0.2224,0.0096</t>
-  </si>
-  <si>
-    <t>0.9453,0.0053,0.0085,0.0101</t>
-  </si>
-  <si>
-    <t>0.8548,0.0200,0.0175,0.0301</t>
-  </si>
-  <si>
-    <t>0.3121,0.5526,0.0028,0.0112</t>
-  </si>
-  <si>
-    <t>0.1325,0.5939,0.0191,0.0824</t>
-  </si>
-  <si>
-    <t>0.0021,0.9660,0.7565,0.0004</t>
+    <t>0.4680,0.1166,0.2225,0.0097</t>
+  </si>
+  <si>
+    <t>0.9451,0.0053,0.0086,0.0101</t>
+  </si>
+  <si>
+    <t>0.8544,0.0200,0.0175,0.0303</t>
+  </si>
+  <si>
+    <t>0.3114,0.5531,0.0028,0.0113</t>
+  </si>
+  <si>
+    <t>0.1322,0.5939,0.0191,0.0828</t>
+  </si>
+  <si>
+    <t>0.0021,0.9659,0.7570,0.0004</t>
   </si>
   <si>
     <t>0.0017,0.0184,0.9915,0.0045</t>
   </si>
   <si>
-    <t>0.0865,0.1821,0.8071,0.0112</t>
-  </si>
-  <si>
-    <t>0.3384,0.0213,0.3082,0.1371</t>
-  </si>
-  <si>
-    <t>0.0038,0.9628,0.3136,0.0059</t>
+    <t>0.0864,0.1820,0.8074,0.0112</t>
+  </si>
+  <si>
+    <t>0.3380,0.0212,0.3085,0.1375</t>
+  </si>
+  <si>
+    <t>0.0038,0.9627,0.3144,0.0059</t>
   </si>
   <si>
     <t>0.0006,0.9949,0.0163,0.0016</t>
   </si>
   <si>
-    <t>0.0188,0.0121,0.9751,0.0015</t>
-  </si>
-  <si>
-    <t>0.0365,0.6590,0.0026,0.4045</t>
+    <t>0.0188,0.0120,0.9752,0.0015</t>
+  </si>
+  <si>
+    <t>0.0363,0.6591,0.0026,0.4060</t>
   </si>
   <si>
     <t>0.0001,0.9998,0.0003,0.0001</t>
@@ -967,55 +973,55 @@
     <t>0.0002,0.9995,0.0030,0.0003</t>
   </si>
   <si>
-    <t>0.0043,0.0362,0.9842,0.0020</t>
-  </si>
-  <si>
-    <t>0.0065,0.1624,0.9407,0.0081</t>
-  </si>
-  <si>
-    <t>0.0539,0.0057,0.9492,0.0016</t>
-  </si>
-  <si>
-    <t>0.3577,0.0006,0.7733,0.0003</t>
-  </si>
-  <si>
-    <t>0.0895,0.0055,0.9215,0.0012</t>
-  </si>
-  <si>
-    <t>0.0943,0.0108,0.9075,0.0026</t>
-  </si>
-  <si>
-    <t>0.9620,0.0171,0.0043,0.0028</t>
+    <t>0.0043,0.0362,0.9843,0.0020</t>
+  </si>
+  <si>
+    <t>0.0065,0.1623,0.9408,0.0081</t>
+  </si>
+  <si>
+    <t>0.0538,0.0057,0.9493,0.0016</t>
+  </si>
+  <si>
+    <t>0.3573,0.0006,0.7735,0.0003</t>
+  </si>
+  <si>
+    <t>0.0894,0.0055,0.9216,0.0012</t>
+  </si>
+  <si>
+    <t>0.0942,0.0108,0.9077,0.0026</t>
+  </si>
+  <si>
+    <t>0.9619,0.0171,0.0043,0.0028</t>
   </si>
   <si>
     <t>0.9867,0.0013,0.0037,0.0021</t>
   </si>
   <si>
-    <t>0.9322,0.0109,0.0034,0.0197</t>
-  </si>
-  <si>
-    <t>0.7904,0.0032,0.0599,0.0254</t>
-  </si>
-  <si>
-    <t>0.9763,0.0014,0.0032,0.0063</t>
-  </si>
-  <si>
-    <t>0.9922,0.0012,0.0020,0.0011</t>
-  </si>
-  <si>
-    <t>0.9386,0.0024,0.0020,0.0291</t>
-  </si>
-  <si>
-    <t>0.0002,0.9964,0.7650,0.0000</t>
+    <t>0.9319,0.0109,0.0034,0.0198</t>
+  </si>
+  <si>
+    <t>0.7897,0.0032,0.0599,0.0256</t>
+  </si>
+  <si>
+    <t>0.9762,0.0014,0.0032,0.0064</t>
+  </si>
+  <si>
+    <t>0.9921,0.0012,0.0020,0.0011</t>
+  </si>
+  <si>
+    <t>0.9383,0.0024,0.0020,0.0293</t>
+  </si>
+  <si>
+    <t>0.0002,0.9964,0.7654,0.0000</t>
   </si>
   <si>
     <t>0.0038,0.0118,0.9940,0.0002</t>
   </si>
   <si>
-    <t>0.0109,0.0372,0.9791,0.0014</t>
-  </si>
-  <si>
-    <t>0.0008,0.9667,0.9283,0.0003</t>
+    <t>0.0108,0.0372,0.9792,0.0014</t>
+  </si>
+  <si>
+    <t>0.0008,0.9666,0.9284,0.0003</t>
   </si>
   <si>
     <t>0.0001,0.0022,0.9994,0.0006</t>
@@ -1024,91 +1030,91 @@
     <t>0.0070,0.9907,0.0027,0.0025</t>
   </si>
   <si>
-    <t>0.0004,0.9992,0.0028,0.0002</t>
-  </si>
-  <si>
-    <t>0.9836,0.0031,0.0075,0.0006</t>
-  </si>
-  <si>
-    <t>0.6023,0.1723,0.1019,0.0115</t>
-  </si>
-  <si>
-    <t>0.4454,0.0079,0.5351,0.0026</t>
-  </si>
-  <si>
-    <t>0.0020,0.9388,0.9098,0.0006</t>
-  </si>
-  <si>
-    <t>0.0018,0.9528,0.9009,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.9983,0.2927,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.9488,0.8964,0.0008</t>
-  </si>
-  <si>
-    <t>0.1505,0.0336,0.0017,0.8431</t>
-  </si>
-  <si>
-    <t>0.0657,0.0176,0.0003,0.9611</t>
-  </si>
-  <si>
-    <t>0.3861,0.0032,0.0003,0.7975</t>
-  </si>
-  <si>
-    <t>0.3647,0.0041,0.0005,0.7907</t>
-  </si>
-  <si>
-    <t>0.3730,0.0319,0.0011,0.4565</t>
-  </si>
-  <si>
-    <t>0.1098,0.0158,0.0005,0.9250</t>
-  </si>
-  <si>
-    <t>0.0008,0.9962,0.3012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.8593,0.9569,0.0005</t>
-  </si>
-  <si>
-    <t>0.0040,0.9485,0.5225,0.0032</t>
-  </si>
-  <si>
-    <t>0.0030,0.7645,0.9524,0.0009</t>
-  </si>
-  <si>
-    <t>0.0002,0.9910,0.9228,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.9916,0.1754,0.0010</t>
+    <t>0.0004,0.9992,0.0029,0.0002</t>
+  </si>
+  <si>
+    <t>0.9836,0.0031,0.0076,0.0006</t>
+  </si>
+  <si>
+    <t>0.6020,0.1722,0.1020,0.0115</t>
+  </si>
+  <si>
+    <t>0.4448,0.0079,0.5358,0.0026</t>
+  </si>
+  <si>
+    <t>0.0020,0.9387,0.9100,0.0006</t>
+  </si>
+  <si>
+    <t>0.0018,0.9528,0.9010,0.0005</t>
+  </si>
+  <si>
+    <t>0.0003,0.9983,0.2934,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.9488,0.8966,0.0008</t>
+  </si>
+  <si>
+    <t>0.1500,0.0335,0.0017,0.8438</t>
+  </si>
+  <si>
+    <t>0.0654,0.0176,0.0003,0.9613</t>
+  </si>
+  <si>
+    <t>0.3850,0.0032,0.0003,0.7984</t>
+  </si>
+  <si>
+    <t>0.3633,0.0040,0.0005,0.7920</t>
+  </si>
+  <si>
+    <t>0.3718,0.0319,0.0011,0.4584</t>
+  </si>
+  <si>
+    <t>0.1093,0.0158,0.0005,0.9254</t>
+  </si>
+  <si>
+    <t>0.0008,0.9962,0.3018,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.8590,0.9569,0.0005</t>
+  </si>
+  <si>
+    <t>0.0040,0.9484,0.5231,0.0032</t>
+  </si>
+  <si>
+    <t>0.0030,0.7643,0.9525,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.9910,0.9229,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.9916,0.1758,0.0010</t>
   </si>
   <si>
     <t>0.9865,0.0041,0.0010,0.0021</t>
   </si>
   <si>
-    <t>0.9642,0.0100,0.0035,0.0050</t>
-  </si>
-  <si>
-    <t>0.9566,0.0214,0.0004,0.0015</t>
-  </si>
-  <si>
-    <t>0.9821,0.0091,0.0009,0.0018</t>
-  </si>
-  <si>
-    <t>0.8948,0.0156,0.0006,0.0275</t>
-  </si>
-  <si>
-    <t>0.9586,0.0099,0.0024,0.0133</t>
-  </si>
-  <si>
-    <t>0.9226,0.0118,0.0030,0.0248</t>
-  </si>
-  <si>
-    <t>0.9319,0.0383,0.0129,0.0017</t>
-  </si>
-  <si>
-    <t>0.9894,0.0014,0.0019,0.0021</t>
+    <t>0.9641,0.0100,0.0035,0.0050</t>
+  </si>
+  <si>
+    <t>0.9564,0.0214,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9820,0.0091,0.0009,0.0018</t>
+  </si>
+  <si>
+    <t>0.8944,0.0156,0.0006,0.0277</t>
+  </si>
+  <si>
+    <t>0.9586,0.0099,0.0024,0.0134</t>
+  </si>
+  <si>
+    <t>0.9223,0.0118,0.0030,0.0250</t>
+  </si>
+  <si>
+    <t>0.9319,0.0382,0.0129,0.0017</t>
+  </si>
+  <si>
+    <t>0.9894,0.0014,0.0019,0.0022</t>
   </si>
   <si>
     <t>0.9943,0.0021,0.0004,0.0012</t>
@@ -1117,31 +1123,31 @@
     <t>0.9907,0.0011,0.0016,0.0021</t>
   </si>
   <si>
-    <t>0.9915,0.0020,0.0007,0.0019</t>
-  </si>
-  <si>
-    <t>0.9558,0.0062,0.0011,0.0134</t>
-  </si>
-  <si>
-    <t>0.9727,0.0112,0.0010,0.0018</t>
-  </si>
-  <si>
-    <t>0.9830,0.0052,0.0007,0.0029</t>
-  </si>
-  <si>
-    <t>0.9796,0.0014,0.0013,0.0080</t>
+    <t>0.9915,0.0020,0.0007,0.0020</t>
+  </si>
+  <si>
+    <t>0.9556,0.0062,0.0011,0.0135</t>
+  </si>
+  <si>
+    <t>0.9726,0.0112,0.0010,0.0018</t>
+  </si>
+  <si>
+    <t>0.9830,0.0052,0.0007,0.0030</t>
+  </si>
+  <si>
+    <t>0.9795,0.0014,0.0013,0.0081</t>
   </si>
   <si>
     <t>0.0090,0.0001,0.9941,0.0000</t>
   </si>
   <si>
-    <t>0.5247,0.0137,0.5164,0.0073</t>
+    <t>0.5239,0.0137,0.5172,0.0073</t>
   </si>
   <si>
     <t>0.9853,0.0004,0.0163,0.0000</t>
   </si>
   <si>
-    <t>0.3102,0.0034,0.7610,0.0012</t>
+    <t>0.3098,0.0034,0.7613,0.0012</t>
   </si>
   <si>
     <t>0.0008,0.9967,0.0003,0.0063</t>
@@ -1150,10 +1156,10 @@
     <t>0.0015,0.9973,0.0009,0.0017</t>
   </si>
   <si>
-    <t>0.0769,0.8452,0.0014,0.0127</t>
-  </si>
-  <si>
-    <t>0.2895,0.6166,0.0018,0.0060</t>
+    <t>0.0768,0.8452,0.0014,0.0127</t>
+  </si>
+  <si>
+    <t>0.2892,0.6167,0.0018,0.0060</t>
   </si>
   <si>
     <t>0.0008,0.9968,0.0008,0.0090</t>
@@ -1162,22 +1168,22 @@
     <t>0.0002,0.9994,0.0002,0.0007</t>
   </si>
   <si>
-    <t>0.9052,0.0779,0.0016,0.0017</t>
-  </si>
-  <si>
-    <t>0.7403,0.0964,0.0606,0.0110</t>
-  </si>
-  <si>
-    <t>0.5120,0.0309,0.4688,0.0069</t>
-  </si>
-  <si>
-    <t>0.8413,0.0217,0.1293,0.0032</t>
-  </si>
-  <si>
-    <t>0.7830,0.0481,0.0975,0.0083</t>
-  </si>
-  <si>
-    <t>0.0009,0.9340,0.1167,0.4337</t>
+    <t>0.9049,0.0780,0.0016,0.0017</t>
+  </si>
+  <si>
+    <t>0.7398,0.0965,0.0607,0.0110</t>
+  </si>
+  <si>
+    <t>0.5118,0.0309,0.4692,0.0069</t>
+  </si>
+  <si>
+    <t>0.8411,0.0217,0.1295,0.0032</t>
+  </si>
+  <si>
+    <t>0.7827,0.0482,0.0977,0.0083</t>
+  </si>
+  <si>
+    <t>0.0009,0.9338,0.1169,0.4342</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0006,0.0000</t>
@@ -1186,28 +1192,28 @@
     <t>0.0000,0.9999,0.0003,0.0001</t>
   </si>
   <si>
-    <t>0.0009,0.9927,0.0009,0.0362</t>
+    <t>0.0009,0.9927,0.0009,0.0363</t>
   </si>
   <si>
     <t>0.0002,0.9994,0.0046,0.0003</t>
   </si>
   <si>
-    <t>0.0096,0.9835,0.0227,0.0079</t>
-  </si>
-  <si>
-    <t>0.4763,0.3190,0.0104,0.0349</t>
-  </si>
-  <si>
-    <t>0.1993,0.5973,0.0037,0.0351</t>
+    <t>0.0096,0.9835,0.0227,0.0080</t>
+  </si>
+  <si>
+    <t>0.4757,0.3192,0.0104,0.0350</t>
+  </si>
+  <si>
+    <t>0.1986,0.5977,0.0037,0.0353</t>
   </si>
   <si>
     <t>0.9944,0.0009,0.0007,0.0010</t>
   </si>
   <si>
-    <t>0.9328,0.0149,0.0004,0.0110</t>
-  </si>
-  <si>
-    <t>0.9809,0.0053,0.0021,0.0030</t>
+    <t>0.9326,0.0149,0.0004,0.0110</t>
+  </si>
+  <si>
+    <t>0.9808,0.0053,0.0021,0.0030</t>
   </si>
   <si>
     <t>0.9865,0.0029,0.0029,0.0020</t>
@@ -1219,115 +1225,115 @@
     <t>0.9766,0.0021,0.0027,0.0070</t>
   </si>
   <si>
-    <t>0.9817,0.0017,0.0023,0.0054</t>
+    <t>0.9816,0.0017,0.0023,0.0054</t>
   </si>
   <si>
     <t>0.9830,0.0010,0.0018,0.0059</t>
   </si>
   <si>
-    <t>0.0058,0.9375,0.7387,0.0023</t>
-  </si>
-  <si>
-    <t>0.0015,0.7170,0.9744,0.0003</t>
-  </si>
-  <si>
-    <t>0.0008,0.0825,0.9945,0.0013</t>
-  </si>
-  <si>
-    <t>0.0773,0.0250,0.9228,0.0018</t>
-  </si>
-  <si>
-    <t>0.9768,0.0039,0.0117,0.0008</t>
-  </si>
-  <si>
-    <t>0.6717,0.1634,0.0325,0.0112</t>
-  </si>
-  <si>
-    <t>0.6023,0.0011,0.4953,0.0004</t>
-  </si>
-  <si>
-    <t>0.8939,0.0257,0.0629,0.0041</t>
-  </si>
-  <si>
-    <t>0.6365,0.0021,0.0004,0.4816</t>
-  </si>
-  <si>
-    <t>0.0027,0.0198,0.0002,0.9984</t>
-  </si>
-  <si>
-    <t>0.0152,0.0114,0.0003,0.9937</t>
-  </si>
-  <si>
-    <t>0.4606,0.0073,0.0007,0.5636</t>
-  </si>
-  <si>
-    <t>0.0009,0.9794,0.8370,0.0002</t>
-  </si>
-  <si>
-    <t>0.9739,0.0033,0.0043,0.0047</t>
-  </si>
-  <si>
-    <t>0.4523,0.3218,0.0039,0.0365</t>
-  </si>
-  <si>
-    <t>0.9784,0.0019,0.0053,0.0036</t>
-  </si>
-  <si>
-    <t>0.5881,0.2461,0.0041,0.0225</t>
-  </si>
-  <si>
-    <t>0.9778,0.0051,0.0028,0.0037</t>
-  </si>
-  <si>
-    <t>0.4104,0.0001,0.6974,0.0000</t>
-  </si>
-  <si>
-    <t>0.5588,0.0002,0.5202,0.0003</t>
+    <t>0.0058,0.9374,0.7392,0.0023</t>
+  </si>
+  <si>
+    <t>0.0015,0.7166,0.9745,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.0824,0.9945,0.0013</t>
+  </si>
+  <si>
+    <t>0.0772,0.0250,0.9229,0.0019</t>
+  </si>
+  <si>
+    <t>0.9767,0.0039,0.0117,0.0008</t>
+  </si>
+  <si>
+    <t>0.6712,0.1636,0.0325,0.0112</t>
+  </si>
+  <si>
+    <t>0.6017,0.0011,0.4959,0.0004</t>
+  </si>
+  <si>
+    <t>0.8937,0.0257,0.0631,0.0041</t>
+  </si>
+  <si>
+    <t>0.6354,0.0021,0.0004,0.4833</t>
+  </si>
+  <si>
+    <t>0.0027,0.0198,0.0002,0.9985</t>
+  </si>
+  <si>
+    <t>0.0151,0.0114,0.0003,0.9937</t>
+  </si>
+  <si>
+    <t>0.4592,0.0073,0.0007,0.5656</t>
+  </si>
+  <si>
+    <t>0.0009,0.9794,0.8373,0.0002</t>
+  </si>
+  <si>
+    <t>0.9738,0.0033,0.0043,0.0048</t>
+  </si>
+  <si>
+    <t>0.4514,0.3221,0.0039,0.0367</t>
+  </si>
+  <si>
+    <t>0.9783,0.0019,0.0053,0.0036</t>
+  </si>
+  <si>
+    <t>0.5874,0.2464,0.0041,0.0227</t>
+  </si>
+  <si>
+    <t>0.9777,0.0051,0.0028,0.0038</t>
+  </si>
+  <si>
+    <t>0.4103,0.0001,0.6975,0.0000</t>
+  </si>
+  <si>
+    <t>0.5582,0.0002,0.5207,0.0003</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.6021,0.0003,0.0014,0.3950</t>
-  </si>
-  <si>
-    <t>0.6548,0.0074,0.0020,0.2976</t>
-  </si>
-  <si>
-    <t>0.4248,0.3267,0.0096,0.0510</t>
-  </si>
-  <si>
-    <t>0.9861,0.0045,0.0031,0.0009</t>
-  </si>
-  <si>
-    <t>0.9369,0.0258,0.0048,0.0061</t>
-  </si>
-  <si>
-    <t>0.4205,0.4209,0.0144,0.0173</t>
+    <t>0.6008,0.0003,0.0014,0.3964</t>
+  </si>
+  <si>
+    <t>0.6536,0.0074,0.0020,0.2991</t>
+  </si>
+  <si>
+    <t>0.4241,0.3268,0.0096,0.0513</t>
+  </si>
+  <si>
+    <t>0.9860,0.0045,0.0031,0.0009</t>
+  </si>
+  <si>
+    <t>0.9367,0.0258,0.0048,0.0061</t>
+  </si>
+  <si>
+    <t>0.4200,0.4211,0.0144,0.0174</t>
   </si>
   <si>
     <t>0.9789,0.0042,0.0105,0.0007</t>
   </si>
   <si>
-    <t>0.9279,0.0340,0.0215,0.0025</t>
+    <t>0.9277,0.0341,0.0216,0.0026</t>
   </si>
   <si>
     <t>0.9894,0.0022,0.0029,0.0012</t>
   </si>
   <si>
-    <t>0.8928,0.0200,0.0006,0.0164</t>
+    <t>0.8923,0.0200,0.0006,0.0165</t>
   </si>
   <si>
     <t>0.9866,0.0018,0.0026,0.0024</t>
   </si>
   <si>
-    <t>0.9620,0.0007,0.0009,0.0226</t>
+    <t>0.9618,0.0007,0.0009,0.0227</t>
   </si>
   <si>
     <t>0.9850,0.0028,0.0033,0.0019</t>
   </si>
   <si>
-    <t>0.9878,0.0040,0.0025,0.0011</t>
+    <t>0.9877,0.0040,0.0025,0.0011</t>
   </si>
   <si>
     <t>0.9885,0.0022,0.0025,0.0014</t>
@@ -1336,157 +1342,157 @@
     <t>0.9876,0.0009,0.0017,0.0032</t>
   </si>
   <si>
-    <t>0.3418,0.4387,0.0046,0.0321</t>
-  </si>
-  <si>
-    <t>0.5818,0.2376,0.0031,0.0181</t>
-  </si>
-  <si>
-    <t>0.2702,0.1981,0.0010,0.1402</t>
-  </si>
-  <si>
-    <t>0.8509,0.0182,0.0594,0.0157</t>
-  </si>
-  <si>
-    <t>0.9641,0.0071,0.0005,0.0083</t>
-  </si>
-  <si>
-    <t>0.8032,0.0477,0.0210,0.0309</t>
-  </si>
-  <si>
-    <t>0.9560,0.0040,0.0010,0.0169</t>
+    <t>0.3411,0.4389,0.0046,0.0322</t>
+  </si>
+  <si>
+    <t>0.5810,0.2379,0.0031,0.0182</t>
+  </si>
+  <si>
+    <t>0.2693,0.1983,0.0010,0.1411</t>
+  </si>
+  <si>
+    <t>0.8505,0.0182,0.0595,0.0158</t>
+  </si>
+  <si>
+    <t>0.9639,0.0071,0.0005,0.0084</t>
+  </si>
+  <si>
+    <t>0.8028,0.0477,0.0211,0.0310</t>
+  </si>
+  <si>
+    <t>0.9558,0.0040,0.0010,0.0170</t>
   </si>
   <si>
     <t>0.9854,0.0073,0.0018,0.0010</t>
   </si>
   <si>
-    <t>0.1661,0.0050,0.8491,0.0023</t>
-  </si>
-  <si>
-    <t>0.9257,0.0166,0.0166,0.0084</t>
+    <t>0.1658,0.0050,0.8493,0.0024</t>
+  </si>
+  <si>
+    <t>0.9255,0.0166,0.0166,0.0084</t>
   </si>
   <si>
     <t>0.0029,0.0013,0.9963,0.0002</t>
   </si>
   <si>
-    <t>0.0021,0.3218,0.8811,0.0101</t>
-  </si>
-  <si>
-    <t>0.2634,0.0676,0.4408,0.0688</t>
-  </si>
-  <si>
-    <t>0.0128,0.1657,0.8967,0.0042</t>
+    <t>0.0021,0.3215,0.8814,0.0100</t>
+  </si>
+  <si>
+    <t>0.2629,0.0676,0.4412,0.0690</t>
+  </si>
+  <si>
+    <t>0.0128,0.1653,0.8969,0.0042</t>
   </si>
   <si>
     <t>0.0130,0.0082,0.9832,0.0010</t>
   </si>
   <si>
-    <t>0.0200,0.0003,0.9872,0.0001</t>
-  </si>
-  <si>
-    <t>0.0820,0.0040,0.9349,0.0011</t>
-  </si>
-  <si>
-    <t>0.4985,0.0358,0.5045,0.0052</t>
-  </si>
-  <si>
-    <t>0.8159,0.0040,0.2060,0.0005</t>
-  </si>
-  <si>
-    <t>0.7429,0.1022,0.0642,0.0076</t>
-  </si>
-  <si>
-    <t>0.5439,0.0579,0.3365,0.0061</t>
-  </si>
-  <si>
-    <t>0.4224,0.0864,0.3899,0.0047</t>
-  </si>
-  <si>
-    <t>0.6327,0.0099,0.3776,0.0015</t>
-  </si>
-  <si>
-    <t>0.7927,0.0250,0.1827,0.0039</t>
-  </si>
-  <si>
-    <t>0.6889,0.0597,0.1981,0.0069</t>
-  </si>
-  <si>
-    <t>0.1114,0.8989,0.0132,0.0045</t>
-  </si>
-  <si>
-    <t>0.5185,0.3343,0.0040,0.0178</t>
-  </si>
-  <si>
-    <t>0.8238,0.0799,0.0057,0.0167</t>
-  </si>
-  <si>
-    <t>0.8385,0.0163,0.0008,0.0628</t>
-  </si>
-  <si>
-    <t>0.7790,0.0896,0.0016,0.0198</t>
-  </si>
-  <si>
-    <t>0.4017,0.5186,0.0152,0.0041</t>
-  </si>
-  <si>
-    <t>0.9665,0.0115,0.0095,0.0017</t>
-  </si>
-  <si>
-    <t>0.6816,0.0831,0.1113,0.0181</t>
-  </si>
-  <si>
-    <t>0.6882,0.0075,0.3343,0.0025</t>
-  </si>
-  <si>
-    <t>0.8612,0.0176,0.0962,0.0055</t>
-  </si>
-  <si>
-    <t>0.1900,0.0054,0.8502,0.0022</t>
-  </si>
-  <si>
-    <t>0.1232,0.0641,0.8257,0.0181</t>
-  </si>
-  <si>
-    <t>0.1384,0.1941,0.6165,0.0146</t>
-  </si>
-  <si>
-    <t>0.0181,0.0387,0.9732,0.0023</t>
+    <t>0.0199,0.0003,0.9873,0.0001</t>
+  </si>
+  <si>
+    <t>0.0819,0.0040,0.9350,0.0011</t>
+  </si>
+  <si>
+    <t>0.4983,0.0358,0.5048,0.0052</t>
+  </si>
+  <si>
+    <t>0.8157,0.0040,0.2062,0.0005</t>
+  </si>
+  <si>
+    <t>0.7427,0.1022,0.0643,0.0076</t>
+  </si>
+  <si>
+    <t>0.5436,0.0579,0.3367,0.0062</t>
+  </si>
+  <si>
+    <t>0.4220,0.0864,0.3904,0.0047</t>
+  </si>
+  <si>
+    <t>0.6324,0.0099,0.3781,0.0015</t>
+  </si>
+  <si>
+    <t>0.7926,0.0250,0.1829,0.0039</t>
+  </si>
+  <si>
+    <t>0.6888,0.0598,0.1982,0.0069</t>
+  </si>
+  <si>
+    <t>0.1113,0.8989,0.0132,0.0046</t>
+  </si>
+  <si>
+    <t>0.5179,0.3346,0.0040,0.0179</t>
+  </si>
+  <si>
+    <t>0.8234,0.0800,0.0057,0.0168</t>
+  </si>
+  <si>
+    <t>0.8379,0.0163,0.0008,0.0632</t>
+  </si>
+  <si>
+    <t>0.7785,0.0897,0.0016,0.0199</t>
+  </si>
+  <si>
+    <t>0.4014,0.5186,0.0152,0.0041</t>
+  </si>
+  <si>
+    <t>0.9664,0.0115,0.0096,0.0017</t>
+  </si>
+  <si>
+    <t>0.6812,0.0831,0.1114,0.0182</t>
+  </si>
+  <si>
+    <t>0.6878,0.0075,0.3348,0.0025</t>
+  </si>
+  <si>
+    <t>0.8609,0.0176,0.0964,0.0055</t>
+  </si>
+  <si>
+    <t>0.1898,0.0054,0.8503,0.0022</t>
+  </si>
+  <si>
+    <t>0.1230,0.0640,0.8261,0.0181</t>
+  </si>
+  <si>
+    <t>0.1383,0.1937,0.6172,0.0146</t>
+  </si>
+  <si>
+    <t>0.0180,0.0386,0.9733,0.0023</t>
   </si>
   <si>
     <t>0.0364,0.0384,0.9439,0.0044</t>
   </si>
   <si>
-    <t>0.9671,0.0013,0.0012,0.0154</t>
-  </si>
-  <si>
-    <t>0.9638,0.0094,0.0018,0.0075</t>
-  </si>
-  <si>
-    <t>0.9139,0.0323,0.0033,0.0135</t>
-  </si>
-  <si>
-    <t>0.9359,0.0184,0.0006,0.0088</t>
-  </si>
-  <si>
-    <t>0.9783,0.0085,0.0014,0.0028</t>
-  </si>
-  <si>
-    <t>0.9819,0.0055,0.0014,0.0028</t>
-  </si>
-  <si>
-    <t>0.9571,0.0073,0.0030,0.0110</t>
-  </si>
-  <si>
-    <t>0.8972,0.0016,0.0010,0.0820</t>
-  </si>
-  <si>
-    <t>0.5277,0.0035,0.5176,0.0047</t>
-  </si>
-  <si>
-    <t>0.5714,0.1092,0.1387,0.0231</t>
-  </si>
-  <si>
-    <t>0.7910,0.0244,0.1060,0.0138</t>
+    <t>0.9669,0.0013,0.0012,0.0155</t>
+  </si>
+  <si>
+    <t>0.9637,0.0094,0.0018,0.0076</t>
+  </si>
+  <si>
+    <t>0.9136,0.0324,0.0033,0.0135</t>
+  </si>
+  <si>
+    <t>0.9357,0.0185,0.0006,0.0089</t>
+  </si>
+  <si>
+    <t>0.9782,0.0086,0.0014,0.0028</t>
+  </si>
+  <si>
+    <t>0.9819,0.0055,0.0014,0.0029</t>
+  </si>
+  <si>
+    <t>0.9570,0.0074,0.0030,0.0110</t>
+  </si>
+  <si>
+    <t>0.8966,0.0016,0.0010,0.0826</t>
+  </si>
+  <si>
+    <t>0.5268,0.0035,0.5182,0.0047</t>
+  </si>
+  <si>
+    <t>0.5707,0.1093,0.1390,0.0232</t>
+  </si>
+  <si>
+    <t>0.7906,0.0244,0.1061,0.0138</t>
   </si>
   <si>
     <t>0.0023,0.0016,0.9970,0.0002</t>
@@ -1495,97 +1501,97 @@
     <t>0.0022,0.0076,0.9946,0.0006</t>
   </si>
   <si>
-    <t>0.0969,0.0590,0.8577,0.0043</t>
+    <t>0.0967,0.0590,0.8580,0.0043</t>
   </si>
   <si>
     <t>0.0002,0.0001,0.9996,0.0000</t>
   </si>
   <si>
-    <t>0.2402,0.0189,0.7714,0.0014</t>
+    <t>0.2400,0.0189,0.7716,0.0014</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0246,0.0169,0.9691,0.0015</t>
-  </si>
-  <si>
-    <t>0.2479,0.2539,0.3232,0.0162</t>
-  </si>
-  <si>
-    <t>0.9435,0.0027,0.0540,0.0005</t>
-  </si>
-  <si>
-    <t>0.9502,0.0025,0.0454,0.0008</t>
-  </si>
-  <si>
-    <t>0.9723,0.0060,0.0131,0.0006</t>
-  </si>
-  <si>
-    <t>0.8786,0.0056,0.0002,0.0660</t>
-  </si>
-  <si>
-    <t>0.9539,0.0196,0.0006,0.0038</t>
-  </si>
-  <si>
-    <t>0.9793,0.0033,0.0019,0.0054</t>
-  </si>
-  <si>
-    <t>0.9225,0.0280,0.0031,0.0116</t>
-  </si>
-  <si>
-    <t>0.6963,0.0035,0.0002,0.3593</t>
-  </si>
-  <si>
-    <t>0.9619,0.0155,0.0016,0.0048</t>
+    <t>0.0246,0.0169,0.9692,0.0015</t>
+  </si>
+  <si>
+    <t>0.2478,0.2537,0.3233,0.0162</t>
+  </si>
+  <si>
+    <t>0.9434,0.0027,0.0541,0.0005</t>
+  </si>
+  <si>
+    <t>0.9501,0.0025,0.0455,0.0008</t>
+  </si>
+  <si>
+    <t>0.9722,0.0060,0.0131,0.0006</t>
+  </si>
+  <si>
+    <t>0.8781,0.0056,0.0002,0.0665</t>
+  </si>
+  <si>
+    <t>0.9538,0.0196,0.0006,0.0038</t>
+  </si>
+  <si>
+    <t>0.9792,0.0033,0.0019,0.0054</t>
+  </si>
+  <si>
+    <t>0.9224,0.0281,0.0031,0.0116</t>
+  </si>
+  <si>
+    <t>0.6952,0.0035,0.0002,0.3612</t>
+  </si>
+  <si>
+    <t>0.9618,0.0155,0.0016,0.0049</t>
   </si>
   <si>
     <t>0.9814,0.0075,0.0016,0.0022</t>
   </si>
   <si>
-    <t>0.8948,0.0169,0.0016,0.0338</t>
-  </si>
-  <si>
-    <t>0.0846,0.0977,0.8354,0.0030</t>
-  </si>
-  <si>
-    <t>0.0129,0.0325,0.9801,0.0009</t>
+    <t>0.8944,0.0170,0.0016,0.0340</t>
+  </si>
+  <si>
+    <t>0.0845,0.0975,0.8357,0.0030</t>
+  </si>
+  <si>
+    <t>0.0129,0.0325,0.9802,0.0009</t>
   </si>
   <si>
     <t>0.0132,0.0073,0.9848,0.0004</t>
   </si>
   <si>
-    <t>0.2056,0.0550,0.7468,0.0034</t>
-  </si>
-  <si>
-    <t>0.0551,0.0013,0.9547,0.0007</t>
-  </si>
-  <si>
-    <t>0.4240,0.0828,0.0113,0.1513</t>
-  </si>
-  <si>
-    <t>0.3356,0.0934,0.2970,0.1003</t>
+    <t>0.2054,0.0550,0.7471,0.0034</t>
+  </si>
+  <si>
+    <t>0.0550,0.0013,0.9548,0.0007</t>
+  </si>
+  <si>
+    <t>0.4235,0.0827,0.0113,0.1519</t>
+  </si>
+  <si>
+    <t>0.3353,0.0933,0.2973,0.1005</t>
   </si>
   <si>
     <t>0.0013,0.0077,0.9935,0.0044</t>
   </si>
   <si>
-    <t>0.9785,0.0033,0.0018,0.0053</t>
-  </si>
-  <si>
-    <t>0.0287,0.0953,0.0005,0.9430</t>
-  </si>
-  <si>
-    <t>0.7855,0.0061,0.0007,0.1539</t>
-  </si>
-  <si>
-    <t>0.0005,0.0168,0.0042,0.9994</t>
-  </si>
-  <si>
-    <t>0.0172,0.0115,0.0004,0.9909</t>
-  </si>
-  <si>
-    <t>0.8028,0.0518,0.0074,0.0339</t>
+    <t>0.9784,0.0033,0.0018,0.0053</t>
+  </si>
+  <si>
+    <t>0.0286,0.0953,0.0005,0.9432</t>
+  </si>
+  <si>
+    <t>0.7847,0.0061,0.0007,0.1547</t>
+  </si>
+  <si>
+    <t>0.0005,0.0167,0.0042,0.9994</t>
+  </si>
+  <si>
+    <t>0.0171,0.0115,0.0004,0.9910</t>
+  </si>
+  <si>
+    <t>0.8023,0.0519,0.0074,0.0340</t>
   </si>
 </sst>
 </file>
@@ -1971,7 +1977,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1982,10 +1988,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1999,7 +2005,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2013,7 +2019,7 @@
         <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2027,7 +2033,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2041,7 +2047,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2055,7 +2061,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2069,7 +2075,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2083,7 +2089,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2097,7 +2103,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2111,7 +2117,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2125,7 +2131,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2139,7 +2145,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2150,10 +2156,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2167,7 +2173,7 @@
         <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2181,7 +2187,7 @@
         <v>264</v>
       </c>
       <c r="D17" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2195,7 +2201,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2206,10 +2212,10 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2220,10 +2226,10 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D20" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2234,10 +2240,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D21" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2248,10 +2254,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2262,10 +2268,10 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D23" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2279,7 +2285,7 @@
         <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2290,10 +2296,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D25" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2304,10 +2310,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D26" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2318,10 +2324,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D27" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2332,10 +2338,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D28" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2346,10 +2352,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D29" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2360,10 +2366,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D30" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2377,7 +2383,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2391,7 +2397,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2402,10 +2408,10 @@
         <v>261</v>
       </c>
       <c r="C33" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2416,10 +2422,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D34" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2433,7 +2439,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2447,7 +2453,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2458,10 +2464,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D37" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2472,10 +2478,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D38" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2486,10 +2492,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D39" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2500,10 +2506,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D40" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2514,10 +2520,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D41" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2528,10 +2534,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D42" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2542,10 +2548,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D43" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2556,10 +2562,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D44" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2570,10 +2576,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D45" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2584,10 +2590,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2598,10 +2604,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D47" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2612,10 +2618,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D48" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2626,10 +2632,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D49" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2640,10 +2646,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D50" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2654,10 +2660,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D51" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2668,10 +2674,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D52" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2682,10 +2688,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D53" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2696,10 +2702,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D54" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2710,10 +2716,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D55" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2727,7 +2733,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2741,7 +2747,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2755,7 +2761,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2769,7 +2775,7 @@
         <v>264</v>
       </c>
       <c r="D59" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2783,7 +2789,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2797,7 +2803,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2811,7 +2817,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2822,10 +2828,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D63" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2836,10 +2842,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D64" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2850,10 +2856,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D65" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2864,10 +2870,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D66" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2878,10 +2884,10 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D67" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2892,10 +2898,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D68" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2906,10 +2912,10 @@
         <v>262</v>
       </c>
       <c r="C69" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D69" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2923,7 +2929,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2937,7 +2943,7 @@
         <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2948,10 +2954,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D72" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2962,10 +2968,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D73" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2976,10 +2982,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D74" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2990,10 +2996,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D75" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3004,10 +3010,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D76" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3018,10 +3024,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D77" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3032,10 +3038,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D78" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3046,10 +3052,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D79" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3060,10 +3066,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D80" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3074,10 +3080,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3088,10 +3094,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D82" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3102,10 +3108,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D83" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3116,10 +3122,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D84" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3130,10 +3136,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D85" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3144,10 +3150,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D86" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3158,10 +3164,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D87" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3172,10 +3178,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D88" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3189,7 +3195,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3203,7 +3209,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3217,7 +3223,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3231,7 +3237,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3245,7 +3251,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3259,7 +3265,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3273,7 +3279,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3287,7 +3293,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3301,7 +3307,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3315,7 +3321,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3329,7 +3335,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3343,7 +3349,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3357,7 +3363,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3371,7 +3377,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3385,7 +3391,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3399,7 +3405,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3410,10 +3416,10 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D105" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3424,10 +3430,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D106" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3441,7 +3447,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3452,10 +3458,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D108" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3466,10 +3472,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D109" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3480,10 +3486,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D110" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3494,10 +3500,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D111" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3508,10 +3514,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D112" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3522,10 +3528,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D113" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3536,10 +3542,10 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D114" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3553,7 +3559,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3567,7 +3573,7 @@
         <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3581,7 +3587,7 @@
         <v>264</v>
       </c>
       <c r="D117" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3595,7 +3601,7 @@
         <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3609,7 +3615,7 @@
         <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3620,10 +3626,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D120" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3634,10 +3640,10 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D121" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3648,10 +3654,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D122" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3662,10 +3668,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D123" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3676,10 +3682,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D124" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3690,10 +3696,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D125" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3704,10 +3710,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D126" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3718,10 +3724,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3735,7 +3741,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3749,7 +3755,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3763,7 +3769,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3777,7 +3783,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3791,7 +3797,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3805,7 +3811,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3819,7 +3825,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3833,7 +3839,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3844,10 +3850,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D136" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3858,10 +3864,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D137" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3872,10 +3878,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D138" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3886,10 +3892,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D139" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3903,7 +3909,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3917,7 +3923,7 @@
         <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3931,7 +3937,7 @@
         <v>264</v>
       </c>
       <c r="D142" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3945,7 +3951,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3959,7 +3965,7 @@
         <v>264</v>
       </c>
       <c r="D144" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3970,10 +3976,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D145" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3984,10 +3990,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3998,10 +4004,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D147" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4012,10 +4018,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4029,7 +4035,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4040,10 +4046,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D150" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4057,7 +4063,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4071,7 +4077,7 @@
         <v>264</v>
       </c>
       <c r="D152" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4085,7 +4091,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4096,10 +4102,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D154" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4110,10 +4116,10 @@
         <v>259</v>
       </c>
       <c r="C155" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D155" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4124,10 +4130,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D156" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4141,7 +4147,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4155,7 +4161,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4166,10 +4172,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D159" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4183,7 +4189,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4197,7 +4203,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4208,10 +4214,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D162" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4225,7 +4231,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4239,7 +4245,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4253,7 +4259,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4267,7 +4273,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4281,7 +4287,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4295,7 +4301,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4309,7 +4315,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4323,7 +4329,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4337,7 +4343,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4351,7 +4357,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4362,10 +4368,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D173" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4379,7 +4385,7 @@
         <v>264</v>
       </c>
       <c r="D174" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4390,10 +4396,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D175" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4407,7 +4413,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4421,7 +4427,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4435,7 +4441,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4449,7 +4455,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4463,7 +4469,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4474,10 +4480,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D181" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4491,7 +4497,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4502,10 +4508,10 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D183" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4516,10 +4522,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D184" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4530,10 +4536,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D185" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4544,10 +4550,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D186" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4558,10 +4564,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D187" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4572,10 +4578,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D188" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4586,10 +4592,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D189" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4600,10 +4606,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D190" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4617,7 +4623,7 @@
         <v>264</v>
       </c>
       <c r="D191" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4631,7 +4637,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4645,7 +4651,7 @@
         <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4656,10 +4662,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D194" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4673,7 +4679,7 @@
         <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4687,7 +4693,7 @@
         <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4701,7 +4707,7 @@
         <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4712,10 +4718,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D198" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4729,7 +4735,7 @@
         <v>264</v>
       </c>
       <c r="D199" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4743,7 +4749,7 @@
         <v>264</v>
       </c>
       <c r="D200" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4757,7 +4763,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4771,7 +4777,7 @@
         <v>264</v>
       </c>
       <c r="D202" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4782,10 +4788,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D203" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4799,7 +4805,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4813,7 +4819,7 @@
         <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4827,7 +4833,7 @@
         <v>264</v>
       </c>
       <c r="D206" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4841,7 +4847,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4852,10 +4858,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D208" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4866,10 +4872,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D209" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4880,10 +4886,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D210" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4894,10 +4900,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D211" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4908,10 +4914,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D212" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4925,7 +4931,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4939,7 +4945,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4953,7 +4959,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4967,7 +4973,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4981,7 +4987,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4995,7 +5001,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5009,7 +5015,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5023,7 +5029,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5034,10 +5040,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D221" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5051,7 +5057,7 @@
         <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5065,7 +5071,7 @@
         <v>264</v>
       </c>
       <c r="D223" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5076,10 +5082,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D224" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5090,10 +5096,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D225" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5104,10 +5110,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D226" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5118,10 +5124,10 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D227" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5132,10 +5138,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D228" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5146,10 +5152,10 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D229" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5160,10 +5166,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D230" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5174,10 +5180,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D231" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5191,7 +5197,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5205,7 +5211,7 @@
         <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5219,7 +5225,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5233,7 +5239,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5247,7 +5253,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5261,7 +5267,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5275,7 +5281,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5289,7 +5295,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5303,7 +5309,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5317,7 +5323,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5331,7 +5337,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5342,10 +5348,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D243" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5356,10 +5362,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D244" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5370,10 +5376,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D245" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5384,10 +5390,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D246" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5398,10 +5404,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D247" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5412,10 +5418,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D248" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5426,10 +5432,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D249" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5440,10 +5446,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D250" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5457,7 +5463,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5468,10 +5474,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D252" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5485,7 +5491,7 @@
         <v>264</v>
       </c>
       <c r="D253" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5496,10 +5502,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D254" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5510,10 +5516,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D255" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5527,7 +5533,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
